--- a/data/tables/sample_maintenance_history.xlsx
+++ b/data/tables/sample_maintenance_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Record ID</t>
   </si>
@@ -34,6 +34,12 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Cost_INR</t>
+  </si>
+  <si>
+    <t>Downtime_Hrs</t>
+  </si>
+  <si>
     <t>REC-8841</t>
   </si>
   <si>
@@ -67,7 +73,7 @@
     <t>Routine Lubrication &amp; Vibration Check</t>
   </si>
   <si>
-    <t>Coupling Alignment</t>
+    <t>Coupling Alignment &amp; Shimming</t>
   </si>
   <si>
     <t>Oil Top-up &amp; Gasket Inspection</t>
@@ -417,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,85 +445,115 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <v>42000</v>
+      </c>
+      <c r="H2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3">
+        <v>8500</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>15000</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>6200</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
